--- a/data/trans_camb/IP7_R-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/IP7_R-Provincia-trans_camb.xlsx
@@ -614,7 +614,7 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>Almeria</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-6,69; 6,95</t>
+          <t>-7,05; 6,32</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-4,49; 11,91</t>
+          <t>-4,88; 10,69</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-2,02; 32,25</t>
+          <t>-1,54; 33,48</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-2,4; 8,98</t>
+          <t>-2,42; 9,03</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-0,81; 11,69</t>
+          <t>-0,94; 11,46</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-1,78; 9,59</t>
+          <t>-1,77; 9,82</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-3,18; 5,55</t>
+          <t>-3,51; 5,37</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-0,71; 9,18</t>
+          <t>-0,54; 9,11</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-0,03; 17,76</t>
+          <t>0,36; 19,42</t>
         </is>
       </c>
     </row>
@@ -783,17 +783,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-84,03; 400,83</t>
+          <t>-90,56; 405,33</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-66,93; 692,54</t>
+          <t>-67,57; 489,27</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-52,58; inf</t>
+          <t>-44,56; 2574,36</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -803,34 +803,34 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-69,64; —</t>
+          <t>-66,49; —</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-77,73; —</t>
+          <t>-80,89; —</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-63,63; 288,64</t>
+          <t>-65,88; 280,64</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-22,82; 468,72</t>
+          <t>-23,76; 498,21</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-28,49; 777,81</t>
+          <t>-16,92; 904,72</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>Cadiz</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-1,82; 4,95</t>
+          <t>-1,8; 4,96</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-2,5; 3,94</t>
+          <t>-2,58; 3,89</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-2,47; 4,82</t>
+          <t>-2,26; 4,37</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-4,09; 4,05</t>
+          <t>-3,63; 4,95</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-5,18; 3,32</t>
+          <t>-4,95; 3,6</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-6,38; 0,98</t>
+          <t>-6,62; 0,86</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-2,13; 3,13</t>
+          <t>-2,09; 3,32</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-2,76; 2,62</t>
+          <t>-2,91; 2,7</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-3,43; 1,66</t>
+          <t>-3,1; 1,95</t>
         </is>
       </c>
     </row>
@@ -999,7 +999,7 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-85,61; 803,71</t>
+          <t>-81,42; —</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -1009,44 +1009,44 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; 772,68</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-69,01; 219,73</t>
+          <t>-65,41; 265,86</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-83,86; 174,88</t>
+          <t>-77,69; 202,78</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 97,37</t>
+          <t>-93,73; 106,61</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-52,46; 192,79</t>
+          <t>-53,07; 163,31</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-68,48; 171,57</t>
+          <t>-69,66; 152,77</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-76,37; 102,15</t>
+          <t>-73,86; 106,7</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>Cordoba</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-3,61; 2,21</t>
+          <t>-3,57; 2,18</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-5,83; 0,0</t>
+          <t>-5,2; 0,0</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-5,88; 0,0</t>
+          <t>-5,85; 0,0</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-5,27; 1,65</t>
+          <t>-5,39; 1,01</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-7,08; -0,87</t>
+          <t>-7,02; -0,86</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-4,12; 4,07</t>
+          <t>-4,38; 4,04</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-3,32; 1,47</t>
+          <t>-3,46; 1,11</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-4,81; -0,45</t>
+          <t>-4,7; -0,45</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-3,31; 1,96</t>
+          <t>-3,11; 1,9</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>1,04; 9,16</t>
+          <t>1,12; 8,93</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>1,5; 9,24</t>
+          <t>1,49; 9,55</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1,15; 10,57</t>
+          <t>1,15; 10,71</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-6,77; 0,87</t>
+          <t>-7,37; 1,05</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-5,18; 4,81</t>
+          <t>-5,76; 4,63</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-5,87; 5,14</t>
+          <t>-5,97; 4,33</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-2,14; 3,38</t>
+          <t>-2,03; 3,4</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-0,81; 5,27</t>
+          <t>-0,8; 5,09</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-1,69; 5,47</t>
+          <t>-1,58; 4,94</t>
         </is>
       </c>
     </row>
@@ -1461,17 +1461,17 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-75,0; 597,21</t>
+          <t>-75,07; 497,27</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-46,27; 816,56</t>
+          <t>-49,46; 918,52</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-79,17; 647,8</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-12,58; -1,48</t>
+          <t>-11,47; -1,48</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-12,75; -1,49</t>
+          <t>-11,07; -1,47</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-10,51; 1,66</t>
+          <t>-9,57; 1,84</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-9,86; 7,27</t>
+          <t>-9,53; 8,34</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-15,65; -3,1</t>
+          <t>-15,68; -3,06</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-14,16; -0,2</t>
+          <t>-14,07; -0,23</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-7,46; 2,44</t>
+          <t>-8,16; 2,5</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-11,97; -3,05</t>
+          <t>-11,82; -3,07</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-10,18; -0,37</t>
+          <t>-9,91; -0,19</t>
         </is>
       </c>
     </row>
@@ -1662,7 +1662,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-81,37; 269,17</t>
+          <t>-82,99; 281,91</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -1677,7 +1677,7 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-86,07; 93,23</t>
+          <t>-83,96; 91,82</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -1687,14 +1687,14 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 45,11</t>
+          <t>-100,0; 53,97</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>Jaen</t>
+          <t>Jaén</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-2,31; 4,08</t>
+          <t>-2,3; 5,07</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-2,3; 3,61</t>
+          <t>-2,32; 4,57</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-2,3; 5,77</t>
+          <t>-2,3; 4,78</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-4,33; 3,37</t>
+          <t>-4,41; 2,44</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-4,28; 3,59</t>
+          <t>-4,3; 3,7</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-3,06; 5,77</t>
+          <t>-2,86; 5,54</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-2,81; 2,15</t>
+          <t>-2,74; 1,98</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-2,79; 2,39</t>
+          <t>-2,78; 2,53</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-2,18; 3,89</t>
+          <t>-1,9; 3,68</t>
         </is>
       </c>
     </row>
@@ -1903,14 +1903,14 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-87,32; —</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>Malaga</t>
+          <t>Málaga</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-1,67; 2,42</t>
+          <t>-1,6; 2,84</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-2,12; 1,48</t>
+          <t>-2,12; 1,86</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-1,04; 4,28</t>
+          <t>-1,21; 4,69</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-3,75; 1,69</t>
+          <t>-3,83; 1,69</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-3,67; 1,93</t>
+          <t>-3,63; 2,23</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-2,13; 4,72</t>
+          <t>-2,36; 4,74</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-2,0; 1,73</t>
+          <t>-2,04; 1,51</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-2,06; 1,21</t>
+          <t>-2,17; 1,33</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-0,95; 3,42</t>
+          <t>-0,88; 3,71</t>
         </is>
       </c>
     </row>
@@ -2089,37 +2089,37 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; —</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-89,31; 255,57</t>
+          <t>-87,52; 278,74</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-87,12; 316,78</t>
+          <t>-87,27; 273,99</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-59,04; 469,49</t>
+          <t>-68,81; 425,74</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-75,46; 211,49</t>
+          <t>-72,13; 166,23</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-77,53; 169,22</t>
+          <t>-79,06; 163,39</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-46,46; 339,43</t>
+          <t>-38,37; 427,43</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-1,12; 4,11</t>
+          <t>-1,14; 3,9</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-2,8; 0,72</t>
+          <t>-2,83; 0,62</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-2,71; 1,43</t>
+          <t>-2,85; 1,13</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-5,41; 0,3</t>
+          <t>-5,49; 0,62</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-6,33; -1,25</t>
+          <t>-6,69; -1,29</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-6,72; -1,21</t>
+          <t>-6,63; -1,07</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>-2,65; 1,18</t>
+          <t>-2,81; 1,21</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>-3,86; -0,65</t>
+          <t>-3,92; -0,74</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>-4,03; -0,7</t>
+          <t>-4,14; -0,69</t>
         </is>
       </c>
     </row>
@@ -2295,7 +2295,7 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>-55,37; 775,38</t>
+          <t>-62,96; 832,05</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
@@ -2310,32 +2310,32 @@
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>-88,55; 35,59</t>
+          <t>-89,18; 69,3</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>-100,0; -12,94</t>
+          <t>-100,0; 10,22</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 8,17</t>
+          <t>-100,0; 50,49</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>-70,16; 81,08</t>
+          <t>-69,34; 70,37</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>-94,86; -24,73</t>
+          <t>-93,9; -25,12</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>-100,0; -9,1</t>
+          <t>-100,0; -6,83</t>
         </is>
       </c>
     </row>
@@ -2405,47 +2405,47 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>-0,6; 1,83</t>
+          <t>-0,54; 1,84</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>-0,97; 1,34</t>
+          <t>-1,0; 1,33</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>-0,08; 4,36</t>
+          <t>-0,11; 4,65</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>-2,51; 0,41</t>
+          <t>-2,48; 0,37</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>-2,99; -0,04</t>
+          <t>-2,86; -0,02</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>-2,74; 0,46</t>
+          <t>-2,52; 0,46</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>-1,15; 0,68</t>
+          <t>-1,18; 0,75</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>-1,49; 0,25</t>
+          <t>-1,58; 0,17</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>-0,84; 1,68</t>
+          <t>-0,93; 1,84</t>
         </is>
       </c>
     </row>
@@ -2511,47 +2511,47 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>-28,29; 162,32</t>
+          <t>-27,26; 157,87</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>-41,59; 117,53</t>
+          <t>-44,5; 113,0</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>-12,81; 350,64</t>
+          <t>-11,13; 340,03</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>-59,51; 14,7</t>
+          <t>-57,91; 15,85</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>-65,92; 3,64</t>
+          <t>-66,7; -0,63</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>-61,17; 20,14</t>
+          <t>-58,11; 20,0</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>-36,2; 31,75</t>
+          <t>-36,41; 35,45</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>-48,15; 13,67</t>
+          <t>-48,32; 9,18</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>-28,71; 74,12</t>
+          <t>-31,55; 76,54</t>
         </is>
       </c>
     </row>
